--- a/Lane-Change/test/Results_Mix_test_FullAndAttackWindow_10s_15s_Attacker_V1.xlsx
+++ b/Lane-Change/test/Results_Mix_test_FullAndAttackWindow_10s_15s_Attacker_V1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="299">
   <si>
     <t>AttackType</t>
   </si>
@@ -710,6 +710,207 @@
   </si>
   <si>
     <t>Max</t>
+  </si>
+  <si>
+    <t>AttackType</t>
+  </si>
+  <si>
+    <t>AttackerVehicle</t>
+  </si>
+  <si>
+    <t>Case</t>
+  </si>
+  <si>
+    <t>Vehicle</t>
+  </si>
+  <si>
+    <t>Full_RMSE_Distance</t>
+  </si>
+  <si>
+    <t>Full_RMSE_Orientation</t>
+  </si>
+  <si>
+    <t>Full_RMSE_Velocity</t>
+  </si>
+  <si>
+    <t>Full_RMSE_Acceleration</t>
+  </si>
+  <si>
+    <t>AttackWindow_RMSE_Distance</t>
+  </si>
+  <si>
+    <t>AttackWindow_RMSE_Orientation</t>
+  </si>
+  <si>
+    <t>AttackWindow_RMSE_Velocity</t>
+  </si>
+  <si>
+    <t>AttackWindow_RMSE_Acceleration</t>
+  </si>
+  <si>
+    <t>Full_Raw_Combined</t>
+  </si>
+  <si>
+    <t>AttackWindow_Raw_Combined</t>
+  </si>
+  <si>
+    <t>RMSE_Window_Start</t>
+  </si>
+  <si>
+    <t>RMSE_Window_End</t>
+  </si>
+  <si>
+    <t>Mean_Trust_Score</t>
+  </si>
+  <si>
+    <t>Trust_Degradation</t>
+  </si>
+  <si>
+    <t>Attack_Detection_Time</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 1</t>
+  </si>
+  <si>
+    <t>V2</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 1</t>
+  </si>
+  <si>
+    <t>V3</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 1</t>
+  </si>
+  <si>
+    <t>V4</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 1</t>
+  </si>
+  <si>
+    <t>V5</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 2</t>
+  </si>
+  <si>
+    <t>V2</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 2</t>
+  </si>
+  <si>
+    <t>V3</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 2</t>
+  </si>
+  <si>
+    <t>V4</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 2</t>
+  </si>
+  <si>
+    <t>V5</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 3</t>
+  </si>
+  <si>
+    <t>V2</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 3</t>
+  </si>
+  <si>
+    <t>V3</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 3</t>
+  </si>
+  <si>
+    <t>V4</t>
+  </si>
+  <si>
+    <t>Mix_test</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Case 3</t>
+  </si>
+  <si>
+    <t>V5</t>
   </si>
 </sst>
 </file>
@@ -781,105 +982,105 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>26</v>
+        <v>232</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>27</v>
+        <v>233</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>28</v>
+        <v>234</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>29</v>
+        <v>235</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>30</v>
+        <v>236</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>31</v>
+        <v>237</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>32</v>
+        <v>238</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>33</v>
+        <v>239</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>34</v>
+        <v>240</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>35</v>
+        <v>241</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>36</v>
+        <v>242</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>37</v>
+        <v>243</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>38</v>
+        <v>244</v>
       </c>
       <c r="N1" s="0" t="s">
-        <v>39</v>
+        <v>245</v>
       </c>
       <c r="O1" s="0" t="s">
-        <v>40</v>
+        <v>246</v>
       </c>
       <c r="P1" s="0" t="s">
-        <v>41</v>
+        <v>247</v>
       </c>
       <c r="Q1" s="0" t="s">
-        <v>42</v>
+        <v>248</v>
       </c>
       <c r="R1" s="0" t="s">
-        <v>43</v>
+        <v>249</v>
       </c>
       <c r="S1" s="0" t="s">
-        <v>44</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>45</v>
+        <v>251</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>46</v>
+        <v>252</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>47</v>
+        <v>253</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>48</v>
+        <v>254</v>
       </c>
       <c r="E2" s="0">
-        <v>0.10787694878958391</v>
+        <v>0.12242065224241105</v>
       </c>
       <c r="F2" s="0">
-        <v>0.018466456474054468</v>
+        <v>0.016599905932937919</v>
       </c>
       <c r="G2" s="0">
-        <v>0.031789028132288281</v>
+        <v>0.029147690186713097</v>
       </c>
       <c r="H2" s="0">
-        <v>0.0042590439612909502</v>
+        <v>0.0042917487540254599</v>
       </c>
       <c r="I2" s="0">
-        <v>0.11156088416635697</v>
+        <v>0.12677967110200311</v>
       </c>
       <c r="J2" s="0">
-        <v>0.020807510805130856</v>
+        <v>0.015216327039717929</v>
       </c>
       <c r="K2" s="0">
-        <v>0.031276491506326325</v>
+        <v>0.027275785328887817</v>
       </c>
       <c r="L2" s="0">
-        <v>0.004410193874032577</v>
+        <v>0.0045169859280707846</v>
       </c>
       <c r="M2" s="0">
-        <v>0.14392502088316314</v>
+        <v>0.15586009118314961</v>
       </c>
       <c r="N2" s="0">
-        <v>0.14724756954671586</v>
+        <v>0.1585724423589617</v>
       </c>
       <c r="O2" s="0">
         <v>10</v>
@@ -888,57 +1089,57 @@
         <v>15</v>
       </c>
       <c r="Q2" s="0">
-        <v>0.35220299532625365</v>
+        <v>0.36337845574288602</v>
       </c>
       <c r="R2" s="0">
-        <v>0.38411227697844685</v>
+        <v>0.41371373969095021</v>
       </c>
       <c r="S2" s="0">
-        <v>10.01</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>49</v>
+        <v>255</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>50</v>
+        <v>256</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>51</v>
+        <v>257</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>52</v>
+        <v>258</v>
       </c>
       <c r="E3" s="0">
-        <v>0.11107462350573115</v>
+        <v>0.11463262569348837</v>
       </c>
       <c r="F3" s="0">
-        <v>0.016969366263658511</v>
+        <v>0.018384913512244517</v>
       </c>
       <c r="G3" s="0">
-        <v>0.029108498884457858</v>
+        <v>0.031901022855357383</v>
       </c>
       <c r="H3" s="0">
-        <v>0.0052157938377802122</v>
+        <v>0.0057042511339161165</v>
       </c>
       <c r="I3" s="0">
-        <v>0.09475503409114007</v>
+        <v>0.10090186455295197</v>
       </c>
       <c r="J3" s="0">
-        <v>0.018945167056433534</v>
+        <v>0.018083967607172777</v>
       </c>
       <c r="K3" s="0">
-        <v>0.02936661292713566</v>
+        <v>0.034625886803835916</v>
       </c>
       <c r="L3" s="0">
-        <v>0.0042205281982351742</v>
+        <v>0.0048980585723218256</v>
       </c>
       <c r="M3" s="0">
-        <v>0.14539891622796922</v>
+        <v>0.15223789968276188</v>
       </c>
       <c r="N3" s="0">
-        <v>0.1283421752165109</v>
+        <v>0.14042580992910969</v>
       </c>
       <c r="O3" s="0">
         <v>10</v>
@@ -947,10 +1148,10 @@
         <v>15</v>
       </c>
       <c r="Q3" s="0">
-        <v>0.23401987814037606</v>
+        <v>0.23226494001063067</v>
       </c>
       <c r="R3" s="0">
-        <v>0.26153870684558456</v>
+        <v>0.26759752656212021</v>
       </c>
       <c r="S3" s="0">
         <v>10</v>
@@ -958,46 +1159,46 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>53</v>
+        <v>259</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>54</v>
+        <v>260</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>55</v>
+        <v>261</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>56</v>
+        <v>262</v>
       </c>
       <c r="E4" s="0">
-        <v>0.11755801638949079</v>
+        <v>0.10977237145752933</v>
       </c>
       <c r="F4" s="0">
-        <v>0.017994685553176855</v>
+        <v>0.019560710414058286</v>
       </c>
       <c r="G4" s="0">
-        <v>0.030556454075454119</v>
+        <v>0.032499235104937504</v>
       </c>
       <c r="H4" s="0">
-        <v>0.0095884378873809552</v>
+        <v>0.008920964263452711</v>
       </c>
       <c r="I4" s="0">
-        <v>0.11004059857575427</v>
+        <v>0.10803570997029083</v>
       </c>
       <c r="J4" s="0">
-        <v>0.020192711424178351</v>
+        <v>0.018745018587560183</v>
       </c>
       <c r="K4" s="0">
-        <v>0.032027784873569644</v>
+        <v>0.033078914463996995</v>
       </c>
       <c r="L4" s="0">
-        <v>0.0036854002972156572</v>
+        <v>0.0055591577512646758</v>
       </c>
       <c r="M4" s="0">
-        <v>0.15770290835232587</v>
+        <v>0.15119257082591955</v>
       </c>
       <c r="N4" s="0">
-        <v>0.14575378374653955</v>
+        <v>0.14667378218555249</v>
       </c>
       <c r="O4" s="0">
         <v>10</v>
@@ -1006,10 +1207,10 @@
         <v>15</v>
       </c>
       <c r="Q4" s="0">
-        <v>0.20808031114624687</v>
+        <v>0.2025791539879101</v>
       </c>
       <c r="R4" s="0">
-        <v>0.22971636090805625</v>
+        <v>0.22812331642142597</v>
       </c>
       <c r="S4" s="0">
         <v>10</v>
@@ -1017,46 +1218,46 @@
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>57</v>
+        <v>263</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>58</v>
+        <v>264</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>59</v>
+        <v>265</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>60</v>
+        <v>266</v>
       </c>
       <c r="E5" s="0">
-        <v>0.11543627965032074</v>
+        <v>0.11755802526792096</v>
       </c>
       <c r="F5" s="0">
-        <v>0.018311987379043743</v>
+        <v>0.017581527262238099</v>
       </c>
       <c r="G5" s="0">
-        <v>0.032169407851735957</v>
+        <v>0.029515800671294543</v>
       </c>
       <c r="H5" s="0">
-        <v>0.013629529479379872</v>
+        <v>0.01222083108023876</v>
       </c>
       <c r="I5" s="0">
-        <v>0.12134198630915843</v>
+        <v>0.12303401072324799</v>
       </c>
       <c r="J5" s="0">
-        <v>0.022509274377053648</v>
+        <v>0.016386355130273044</v>
       </c>
       <c r="K5" s="0">
-        <v>0.03819077025166407</v>
+        <v>0.027474268893814692</v>
       </c>
       <c r="L5" s="0">
-        <v>0.0052948572552506557</v>
+        <v>0.0042549047372119706</v>
       </c>
       <c r="M5" s="0">
-        <v>0.16123521698143659</v>
+        <v>0.15929465701945425</v>
       </c>
       <c r="N5" s="0">
-        <v>0.16482761381607317</v>
+        <v>0.15476318435427464</v>
       </c>
       <c r="O5" s="0">
         <v>10</v>
@@ -1065,10 +1266,10 @@
         <v>15</v>
       </c>
       <c r="Q5" s="0">
-        <v>0.16445164199167825</v>
+        <v>0.16958182949996298</v>
       </c>
       <c r="R5" s="0">
-        <v>0.18413780594436915</v>
+        <v>0.19979176535603621</v>
       </c>
       <c r="S5" s="0">
         <v>10</v>
@@ -1076,46 +1277,46 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>61</v>
+        <v>267</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>62</v>
+        <v>268</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>63</v>
+        <v>269</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>64</v>
+        <v>270</v>
       </c>
       <c r="E6" s="0">
-        <v>0.11421776399445312</v>
+        <v>0.12736352072394322</v>
       </c>
       <c r="F6" s="0">
-        <v>0.019292933159682939</v>
+        <v>0.018799385305907253</v>
       </c>
       <c r="G6" s="0">
-        <v>0.028876321960881104</v>
+        <v>0.032360509393943034</v>
       </c>
       <c r="H6" s="0">
-        <v>0.0039544910343581605</v>
+        <v>0.0042278878368346073</v>
       </c>
       <c r="I6" s="0">
-        <v>0.13219857914441546</v>
+        <v>0.10471750757411225</v>
       </c>
       <c r="J6" s="0">
-        <v>0.018866272112952678</v>
+        <v>0.016714880974499625</v>
       </c>
       <c r="K6" s="0">
-        <v>0.033112574059926209</v>
+        <v>0.031365700272737315</v>
       </c>
       <c r="L6" s="0">
-        <v>0.0035034464203156299</v>
+        <v>0.0045483103738451292</v>
       </c>
       <c r="M6" s="0">
-        <v>0.14704857698969237</v>
+        <v>0.16395191795472086</v>
       </c>
       <c r="N6" s="0">
-        <v>0.16881459962465731</v>
+        <v>0.1406315182206947</v>
       </c>
       <c r="O6" s="0">
         <v>10</v>
@@ -1124,10 +1325,10 @@
         <v>15</v>
       </c>
       <c r="Q6" s="0">
-        <v>0.45783612445667377</v>
+        <v>0.44669759211683169</v>
       </c>
       <c r="R6" s="0">
-        <v>0.098761397733283518</v>
+        <v>0.072243861577983848</v>
       </c>
       <c r="S6" s="0">
         <v>10</v>
@@ -1135,46 +1336,46 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>65</v>
+        <v>271</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>66</v>
+        <v>272</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>67</v>
+        <v>273</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>68</v>
+        <v>274</v>
       </c>
       <c r="E7" s="0">
-        <v>0.11460665740177269</v>
+        <v>0.11402917562107424</v>
       </c>
       <c r="F7" s="0">
-        <v>0.017038595491212963</v>
+        <v>0.017481499578278079</v>
       </c>
       <c r="G7" s="0">
-        <v>0.029322964404586045</v>
+        <v>0.03001844091132112</v>
       </c>
       <c r="H7" s="0">
-        <v>0.0052385368994478376</v>
+        <v>0.0053167122166902694</v>
       </c>
       <c r="I7" s="0">
-        <v>0.1187499709735758</v>
+        <v>0.12410856311364923</v>
       </c>
       <c r="J7" s="0">
-        <v>0.017128396914019732</v>
+        <v>0.016541190775871451</v>
       </c>
       <c r="K7" s="0">
-        <v>0.026548784092511733</v>
+        <v>0.027283158762217586</v>
       </c>
       <c r="L7" s="0">
-        <v>0.0047195662265782099</v>
+        <v>0.004815060602482631</v>
       </c>
       <c r="M7" s="0">
-        <v>0.14916815870580657</v>
+        <v>0.14936432874908565</v>
       </c>
       <c r="N7" s="0">
-        <v>0.15001832129266574</v>
+        <v>0.15620678247834946</v>
       </c>
       <c r="O7" s="0">
         <v>10</v>
@@ -1183,10 +1384,10 @@
         <v>15</v>
       </c>
       <c r="Q7" s="0">
-        <v>0.30597467447939147</v>
+        <v>0.2846206118326729</v>
       </c>
       <c r="R7" s="0">
-        <v>0.027787114919516548</v>
+        <v>0.12921728898037615</v>
       </c>
       <c r="S7" s="0">
         <v>10</v>
@@ -1194,46 +1395,46 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>69</v>
+        <v>275</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>70</v>
+        <v>276</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>71</v>
+        <v>277</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>72</v>
+        <v>278</v>
       </c>
       <c r="E8" s="0">
-        <v>0.11158654704786489</v>
+        <v>0.10883336725774635</v>
       </c>
       <c r="F8" s="0">
-        <v>0.018522727868065806</v>
+        <v>0.018457181341169249</v>
       </c>
       <c r="G8" s="0">
-        <v>0.029281142043845982</v>
+        <v>0.029535010092348549</v>
       </c>
       <c r="H8" s="0">
-        <v>0.0097837887207493993</v>
+        <v>0.0091940160785914191</v>
       </c>
       <c r="I8" s="0">
-        <v>0.11397227272950333</v>
+        <v>0.099945456844494518</v>
       </c>
       <c r="J8" s="0">
-        <v>0.016554760767896495</v>
+        <v>0.017868922809724665</v>
       </c>
       <c r="K8" s="0">
-        <v>0.034665481562631877</v>
+        <v>0.028399419110288038</v>
       </c>
       <c r="L8" s="0">
-        <v>0.0066381622793350217</v>
+        <v>0.0062240339257923823</v>
       </c>
       <c r="M8" s="0">
-        <v>0.15065147781246027</v>
+        <v>0.14756239342868632</v>
       </c>
       <c r="N8" s="0">
-        <v>0.15527591657147025</v>
+        <v>0.13456890988057493</v>
       </c>
       <c r="O8" s="0">
         <v>10</v>
@@ -1242,10 +1443,10 @@
         <v>15</v>
       </c>
       <c r="Q8" s="0">
-        <v>0.28128596377605525</v>
+        <v>0.2614496582476884</v>
       </c>
       <c r="R8" s="0">
-        <v>0.04755273100908719</v>
+        <v>0.070968015944058355</v>
       </c>
       <c r="S8" s="0">
         <v>10</v>
@@ -1253,46 +1454,46 @@
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>73</v>
+        <v>279</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>74</v>
+        <v>280</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>75</v>
+        <v>281</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>76</v>
+        <v>282</v>
       </c>
       <c r="E9" s="0">
-        <v>0.11299569838147189</v>
+        <v>0.12402755094540954</v>
       </c>
       <c r="F9" s="0">
-        <v>0.016452633938077652</v>
+        <v>0.017944269854676745</v>
       </c>
       <c r="G9" s="0">
-        <v>0.028433519492294945</v>
+        <v>0.030408306220863837</v>
       </c>
       <c r="H9" s="0">
-        <v>0.013392013881232789</v>
+        <v>0.013639066361174325</v>
       </c>
       <c r="I9" s="0">
-        <v>0.13026673612191178</v>
+        <v>0.13189237436594003</v>
       </c>
       <c r="J9" s="0">
-        <v>0.017502906127024841</v>
+        <v>0.019611481617964256</v>
       </c>
       <c r="K9" s="0">
-        <v>0.030085187731306622</v>
+        <v>0.030276710191179917</v>
       </c>
       <c r="L9" s="0">
-        <v>0.0088889774784658461</v>
+        <v>0.010141154580146161</v>
       </c>
       <c r="M9" s="0">
-        <v>0.15482123175499962</v>
+        <v>0.16807492352744771</v>
       </c>
       <c r="N9" s="0">
-        <v>0.16924090133168423</v>
+        <v>0.17231023913726612</v>
       </c>
       <c r="O9" s="0">
         <v>10</v>
@@ -1301,10 +1502,10 @@
         <v>15</v>
       </c>
       <c r="Q9" s="0">
-        <v>0.2325949482043542</v>
+        <v>0.20710236341380334</v>
       </c>
       <c r="R9" s="0">
-        <v>0.03321586438211388</v>
+        <v>0.046955335495724726</v>
       </c>
       <c r="S9" s="0">
         <v>10</v>
@@ -1312,46 +1513,46 @@
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>77</v>
+        <v>283</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>78</v>
+        <v>284</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>79</v>
+        <v>285</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>80</v>
+        <v>286</v>
       </c>
       <c r="E10" s="0">
-        <v>0.12812841934480362</v>
+        <v>0.12195891790261587</v>
       </c>
       <c r="F10" s="0">
-        <v>0.01759783303708622</v>
+        <v>0.018549087231812474</v>
       </c>
       <c r="G10" s="0">
-        <v>0.030168281501201363</v>
+        <v>0.031470956096966117</v>
       </c>
       <c r="H10" s="0">
-        <v>0.0041597999818550743</v>
+        <v>0.0042906572209774159</v>
       </c>
       <c r="I10" s="0">
-        <v>0.12266114038678527</v>
+        <v>0.10109141744552086</v>
       </c>
       <c r="J10" s="0">
-        <v>0.017099702118753141</v>
+        <v>0.017212783437588072</v>
       </c>
       <c r="K10" s="0">
-        <v>0.028931714204177842</v>
+        <v>0.03323107567062876</v>
       </c>
       <c r="L10" s="0">
-        <v>0.0034503747826457004</v>
+        <v>0.0048845376109782727</v>
       </c>
       <c r="M10" s="0">
-        <v>0.16245650082786006</v>
+        <v>0.1577205312205594</v>
       </c>
       <c r="N10" s="0">
-        <v>0.15504322937360882</v>
+        <v>0.1392070307271279</v>
       </c>
       <c r="O10" s="0">
         <v>10</v>
@@ -1360,10 +1561,10 @@
         <v>15</v>
       </c>
       <c r="Q10" s="0">
-        <v>0.36535650208023734</v>
+        <v>0.4213975036165436</v>
       </c>
       <c r="R10" s="0">
-        <v>0.40974790208170464</v>
+        <v>0.1781910946194839</v>
       </c>
       <c r="S10" s="0">
         <v>10</v>
@@ -1371,46 +1572,46 @@
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>81</v>
+        <v>287</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>82</v>
+        <v>288</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>83</v>
+        <v>289</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>84</v>
+        <v>290</v>
       </c>
       <c r="E11" s="0">
-        <v>0.11585185047297983</v>
+        <v>0.11857593585709481</v>
       </c>
       <c r="F11" s="0">
-        <v>0.017738995463801845</v>
+        <v>0.018467519652125997</v>
       </c>
       <c r="G11" s="0">
-        <v>0.029164920216506126</v>
+        <v>0.029722489769158641</v>
       </c>
       <c r="H11" s="0">
-        <v>0.0054005900058904481</v>
+        <v>0.0054027888527479976</v>
       </c>
       <c r="I11" s="0">
-        <v>0.10398273359265714</v>
+        <v>0.11369890955959946</v>
       </c>
       <c r="J11" s="0">
-        <v>0.015811154866208706</v>
+        <v>0.017203941051242882</v>
       </c>
       <c r="K11" s="0">
-        <v>0.028746335048647088</v>
+        <v>0.028532153116231994</v>
       </c>
       <c r="L11" s="0">
-        <v>0.0037231763307768668</v>
+        <v>0.005392465200004257</v>
       </c>
       <c r="M11" s="0">
-        <v>0.1504173606953764</v>
+        <v>0.15370121447900145</v>
       </c>
       <c r="N11" s="0">
-        <v>0.13645224497208111</v>
+        <v>0.14762352787583571</v>
       </c>
       <c r="O11" s="0">
         <v>10</v>
@@ -1419,10 +1620,10 @@
         <v>15</v>
       </c>
       <c r="Q11" s="0">
-        <v>0.22983880241752458</v>
+        <v>0.23229903665760895</v>
       </c>
       <c r="R11" s="0">
-        <v>0.25177459838833866</v>
+        <v>0.22223946498875249</v>
       </c>
       <c r="S11" s="0">
         <v>10</v>
@@ -1430,46 +1631,46 @@
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>85</v>
+        <v>291</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>86</v>
+        <v>292</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>87</v>
+        <v>293</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>88</v>
+        <v>294</v>
       </c>
       <c r="E12" s="0">
-        <v>0.12076869881741628</v>
+        <v>0.10791042372791626</v>
       </c>
       <c r="F12" s="0">
-        <v>0.017003777790243556</v>
+        <v>0.018045244243570784</v>
       </c>
       <c r="G12" s="0">
-        <v>0.026748783344187663</v>
+        <v>0.029820537428080027</v>
       </c>
       <c r="H12" s="0">
-        <v>0.0098366585129052338</v>
+        <v>0.0080913919167061622</v>
       </c>
       <c r="I12" s="0">
-        <v>0.10497897265446354</v>
+        <v>0.1173921067433762</v>
       </c>
       <c r="J12" s="0">
-        <v>0.017874938974516304</v>
+        <v>0.016627818784236831</v>
       </c>
       <c r="K12" s="0">
-        <v>0.023275384894621384</v>
+        <v>0.027757538521485742</v>
       </c>
       <c r="L12" s="0">
-        <v>0.0036189964015876331</v>
+        <v>0.0043079011918593126</v>
       </c>
       <c r="M12" s="0">
-        <v>0.15735414067450917</v>
+        <v>0.14582235307270244</v>
       </c>
       <c r="N12" s="0">
-        <v>0.13187335395067257</v>
+        <v>0.14945754645672127</v>
       </c>
       <c r="O12" s="0">
         <v>10</v>
@@ -1478,10 +1679,10 @@
         <v>15</v>
       </c>
       <c r="Q12" s="0">
-        <v>0.21224860898397091</v>
+        <v>0.2060723722770047</v>
       </c>
       <c r="R12" s="0">
-        <v>0.23843658482021984</v>
+        <v>0.18048089665332059</v>
       </c>
       <c r="S12" s="0">
         <v>10</v>
@@ -1489,46 +1690,46 @@
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>89</v>
+        <v>295</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>90</v>
+        <v>296</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>91</v>
+        <v>297</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>92</v>
+        <v>298</v>
       </c>
       <c r="E13" s="0">
-        <v>0.1088786098999345</v>
+        <v>0.1163182096704128</v>
       </c>
       <c r="F13" s="0">
-        <v>0.017378008755420428</v>
+        <v>0.018291312385397621</v>
       </c>
       <c r="G13" s="0">
-        <v>0.028286612156255445</v>
+        <v>0.029429269362088138</v>
       </c>
       <c r="H13" s="0">
-        <v>0.013416130081810966</v>
+        <v>0.011458559337464744</v>
       </c>
       <c r="I13" s="0">
-        <v>0.095872180745488422</v>
+        <v>0.11207714133308699</v>
       </c>
       <c r="J13" s="0">
-        <v>0.014307706123292595</v>
+        <v>0.017641287447229748</v>
       </c>
       <c r="K13" s="0">
-        <v>0.020822391596135477</v>
+        <v>0.024196036750350224</v>
       </c>
       <c r="L13" s="0">
-        <v>0.0062129536328492611</v>
+        <v>0.0050124618006564658</v>
       </c>
       <c r="M13" s="0">
-        <v>0.15058135213800092</v>
+        <v>0.15720603836996566</v>
       </c>
       <c r="N13" s="0">
-        <v>0.12290752597447316</v>
+        <v>0.14128563988409368</v>
       </c>
       <c r="O13" s="0">
         <v>10</v>
@@ -1537,10 +1738,10 @@
         <v>15</v>
       </c>
       <c r="Q13" s="0">
-        <v>0.16567399152467202</v>
+        <v>0.16940180760825033</v>
       </c>
       <c r="R13" s="0">
-        <v>0.17641566938748832</v>
+        <v>0.1438706176324942</v>
       </c>
       <c r="S13" s="0">
         <v>10</v>
